--- a/PLC원본_구ECS_영역매칭표_20260822.xlsx
+++ b/PLC원본_구ECS_영역매칭표_20260822.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\LGLS\Renewal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B40DD547-802A-496D-9484-89DEFBE12FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{557F5659-81DC-41FF-ADD4-C14B12FF5D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{30F2DBE0-EFF0-40FE-BF74-BD8413AA3908}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{30F2DBE0-EFF0-40FE-BF74-BD8413AA3908}"/>
   </bookViews>
   <sheets>
     <sheet name="영역 매칭표" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1379" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="418">
   <si>
     <t>슬라이드</t>
   </si>
@@ -376,9 +376,6 @@
     <t>%DW322</t>
   </si>
   <si>
-    <t>반송 시나리오 (SC_2출고: CV103 CV104)</t>
-  </si>
-  <si>
     <t>M0211</t>
   </si>
   <si>
@@ -508,9 +505,6 @@
     <t>%RB66</t>
   </si>
   <si>
-    <t>PALLET_EXIST01 범위 +1</t>
-  </si>
-  <si>
     <t>R0022</t>
   </si>
   <si>
@@ -532,9 +526,6 @@
     <t>%RB70</t>
   </si>
   <si>
-    <t>PALLET_EXIST02 범위 +1</t>
-  </si>
-  <si>
     <t>M0202</t>
   </si>
   <si>
@@ -583,9 +574,6 @@
     <t>OnWaitOut()</t>
   </si>
   <si>
-    <t>반송 시나리오 (SC_2입고: CV105 CV106)</t>
-  </si>
-  <si>
     <t>M0230</t>
   </si>
   <si>
@@ -670,9 +658,6 @@
     <t>%MX358</t>
   </si>
   <si>
-    <t>반송 시나리오 (SC_3출고: CV107 CV108)</t>
-  </si>
-  <si>
     <t>M0251</t>
   </si>
   <si>
@@ -739,9 +724,6 @@
     <t>%MX390</t>
   </si>
   <si>
-    <t>반송 시나리오 (SC_3입고: CV109 CV110)</t>
-  </si>
-  <si>
     <t>M0270</t>
   </si>
   <si>
@@ -826,9 +808,6 @@
     <t>01A6</t>
   </si>
   <si>
-    <t>반송 시나리오 (SC_4출고: CV111 CV112)</t>
-  </si>
-  <si>
     <t>M0291</t>
   </si>
   <si>
@@ -913,9 +892,6 @@
     <t>01C6</t>
   </si>
   <si>
-    <t>반송 시나리오 (SC_4입고: CV113 CV114)</t>
-  </si>
-  <si>
     <t>M0310</t>
   </si>
   <si>
@@ -991,9 +967,6 @@
     <t>%MX486</t>
   </si>
   <si>
-    <t>반송 시나리오 (SC_5출고: CV115 CV116)</t>
-  </si>
-  <si>
     <t>M0331</t>
   </si>
   <si>
@@ -1063,9 +1036,6 @@
     <t>%MX518</t>
   </si>
   <si>
-    <t>반송 시나리오 (SC_5입고: CV117 CV118)</t>
-  </si>
-  <si>
     <t>M0350</t>
   </si>
   <si>
@@ -1226,6 +1196,118 @@
   </si>
   <si>
     <t>핸들러가 호출하는 업무 함수</t>
+  </si>
+  <si>
+    <t>PLC 원본 Address 표기가 'D0xxx : X' — X 의미 PLC 확인 필요. 구 ECS 는 이 값을 저장·로그만 하고 판정에 쓰지 않음</t>
+  </si>
+  <si>
+    <t>반송 시나리오 (SC_2출고: CV105 CV106)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLC 원본 표기 '반송 시나리오 (SC_2출고: CV103 CV104)' → 창고 Layout(슬3)·구 ECS 기준으로 정정 (원본은 C/V#1 누락으로 트랙 라벨이 2씩 작음)</t>
+  </si>
+  <si>
+    <t>PLC 원본 표기 '반송 시나리오 (SC_2출고: CV103 CV104)' → 창고 Layout(슬3)·구 ECS 기준으로 정정 (원본은 C/V#1 누락으로 트랙 라벨이 2씩 작음)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>반송 시나리오 (SC_2입고: CV107 CV108)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLC 원본 표기 '반송 시나리오 (SC_2입고: CV105 CV106)' → 창고 Layout(슬3)·구 ECS 기준으로 정정 (원본은 C/V#1 누락으로 트랙 라벨이 2씩 작음)</t>
+  </si>
+  <si>
+    <t>PLC 원본 표기 '반송 시나리오 (SC_2입고: CV105 CV106)' → 창고 Layout(슬3)·구 ECS 기준으로 정정 (원본은 C/V#1 누락으로 트랙 라벨이 2씩 작음)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>반송 시나리오 (SC_3출고: CV109 CV110)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLC 원본 표기 '반송 시나리오 (SC_3출고: CV107 CV108)' → 창고 Layout(슬3)·구 ECS 기준으로 정정 (원본은 C/V#1 누락으로 트랙 라벨이 2씩 작음)</t>
+  </si>
+  <si>
+    <t>PLC 원본 표기 '반송 시나리오 (SC_3출고: CV107 CV108)' → 창고 Layout(슬3)·구 ECS 기준으로 정정 (원본은 C/V#1 누락으로 트랙 라벨이 2씩 작음)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>반송 시나리오 (SC_3입고: CV111 CV112)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLC 원본 표기 '반송 시나리오 (SC_3입고: CV109 CV110)' → 창고 Layout(슬3)·구 ECS 기준으로 정정 (원본은 C/V#1 누락으로 트랙 라벨이 2씩 작음)</t>
+  </si>
+  <si>
+    <t>PLC 원본 표기 '반송 시나리오 (SC_3입고: CV109 CV110)' → 창고 Layout(슬3)·구 ECS 기준으로 정정 (원본은 C/V#1 누락으로 트랙 라벨이 2씩 작음)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>반송 시나리오 (SC_4출고: CV113 CV114)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLC 원본 표기 '반송 시나리오 (SC_4출고: CV111 CV112)' → 창고 Layout(슬3)·구 ECS 기준으로 정정 (원본은 C/V#1 누락으로 트랙 라벨이 2씩 작음)</t>
+  </si>
+  <si>
+    <t>PLC 원본 표기 '반송 시나리오 (SC_4출고: CV111 CV112)' → 창고 Layout(슬3)·구 ECS 기준으로 정정 (원본은 C/V#1 누락으로 트랙 라벨이 2씩 작음)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>반송 시나리오 (SC_4입고: CV115 CV116)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLC 원본 표기 '반송 시나리오 (SC_4입고: CV113 CV114)' → 창고 Layout(슬3)·구 ECS 기준으로 정정 (원본은 C/V#1 누락으로 트랙 라벨이 2씩 작음)</t>
+  </si>
+  <si>
+    <t>PLC 원본 표기 '반송 시나리오 (SC_4입고: CV113 CV114)' → 창고 Layout(슬3)·구 ECS 기준으로 정정 (원본은 C/V#1 누락으로 트랙 라벨이 2씩 작음)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>반송 시나리오 (SC_5출고: CV117 CV118)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLC 원본 표기 '반송 시나리오 (SC_5출고: CV115 CV116)' → 창고 Layout(슬3)·구 ECS 기준으로 정정 (원본은 C/V#1 누락으로 트랙 라벨이 2씩 작음)</t>
+  </si>
+  <si>
+    <t>PLC 원본 표기 '반송 시나리오 (SC_5출고: CV115 CV116)' → 창고 Layout(슬3)·구 ECS 기준으로 정정 (원본은 C/V#1 누락으로 트랙 라벨이 2씩 작음)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>반송 시나리오 (SC_5입고: CV119 CV120)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLC 원본 표기 '반송 시나리오 (SC_5입고: CV117 CV118)' → 창고 Layout(슬3)·구 ECS 기준으로 정정 (원본은 C/V#1 누락으로 트랙 라벨이 2씩 작음)</t>
+  </si>
+  <si>
+    <t>PLC 원본 표기 '반송 시나리오 (SC_5입고: CV117 CV118)' → 창고 Layout(슬3)·구 ECS 기준으로 정정 (원본은 C/V#1 누락으로 트랙 라벨이 2씩 작음)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[2026-08-22 정정 내역]</t>
+  </si>
+  <si>
+    <t>① 트랙 라벨</t>
+  </si>
+  <si>
+    <t>PLC 원본은 C/V#1(트랙 101/102)을 누락해 C/V#3 이후 트랙 라벨이 2씩 작게 적혀 있었다. 창고 Layout(슬라이드3)·구 ECS 화면 배치 기준으로 정정.</t>
+  </si>
+  <si>
+    <t>② 주소는 정상</t>
+  </si>
+  <si>
+    <t>설비번호(C/V #N)와 S/C 배정, M/D/R 주소는 원본과 구 ECS 가 일치한다(120개 전수 대조 불일치 0건). 정정 대상은 화면 표기용 트랙 라벨뿐.</t>
+  </si>
+  <si>
+    <t>③ 미확인 사항</t>
+  </si>
+  <si>
+    <t>Reset Alarm Code 의 'D0xxx : X' 에서 X 의 의미, 통로 C/V 슬라이드의 Direction Mode Check 취소선 — PLC 확인 필요 (원본 PPT V1.2 에 붉은 질의 표기)</t>
   </si>
 </sst>
 </file>
@@ -1976,7 +2058,9 @@
       <c r="M7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="N7" s="2"/>
+      <c r="N7" s="2" t="s">
+        <v>386</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
@@ -2228,7 +2312,9 @@
       <c r="M13" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="N13" s="2"/>
+      <c r="N13" s="2" t="s">
+        <v>386</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
@@ -2480,7 +2566,9 @@
       <c r="M19" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="N19" s="2"/>
+      <c r="N19" s="2" t="s">
+        <v>386</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
@@ -2732,7 +2820,9 @@
       <c r="M25" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="N25" s="2"/>
+      <c r="N25" s="2" t="s">
+        <v>386</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
@@ -2984,342 +3074,358 @@
       <c r="M31" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="N31" s="2"/>
+      <c r="N31" s="2" t="s">
+        <v>386</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>8</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E32" s="2" t="s">
+      <c r="F32" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="G32" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="H32" s="2">
         <v>151</v>
       </c>
       <c r="I32" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J32" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="J32" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="K32" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L32" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="L32" s="2" t="s">
+      <c r="M32" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="M32" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="N32" s="2"/>
+      <c r="N32" s="2" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>8</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>112</v>
+        <v>387</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E33" s="2" t="s">
+      <c r="F33" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="H33" s="2">
         <v>144</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J33" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L33" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="K33" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L33" s="2" t="s">
+      <c r="M33" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="M33" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="N33" s="2"/>
+      <c r="N33" s="2" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>8</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>112</v>
+        <v>387</v>
       </c>
       <c r="C34" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E34" s="2" t="s">
+      <c r="F34" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G34" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="H34" s="2">
         <v>524</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J34" s="2"/>
       <c r="K34" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>126</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>8</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>112</v>
+        <v>387</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E35" s="2" t="s">
+      <c r="F35" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="G35" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="H35" s="2">
         <v>189</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J35" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L35" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="K35" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L35" s="2" t="s">
+      <c r="M35" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="M35" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="N35" s="2"/>
+      <c r="N35" s="2" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>8</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>112</v>
+        <v>387</v>
       </c>
       <c r="C36" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E36" s="2" t="s">
+      <c r="F36" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="F36" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="G36" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H36" s="2">
         <v>129</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J36" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L36" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="K36" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L36" s="2" t="s">
+      <c r="M36" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="M36" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="N36" s="2"/>
+      <c r="N36" s="2" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>8</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>112</v>
+        <v>387</v>
       </c>
       <c r="C37" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E37" s="2" t="s">
+      <c r="F37" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="H37" s="2">
         <v>150</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J37" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L37" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="K37" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="M37" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>120</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>8</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>112</v>
+        <v>387</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="E38" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="F38" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="H38" s="2">
         <v>20</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J38" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L38" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L38" s="2" t="s">
+      <c r="M38" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="N38" s="2"/>
+      <c r="N38" s="2" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>8</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>112</v>
+        <v>387</v>
       </c>
       <c r="C39" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="F39" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H39" s="2">
         <v>20</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J39" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L39" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="K39" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L39" s="2" t="s">
+      <c r="M39" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="M39" s="2" t="s">
-        <v>153</v>
-      </c>
       <c r="N39" s="2" t="s">
-        <v>156</v>
+        <v>389</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
@@ -3327,85 +3433,87 @@
         <v>8</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>112</v>
+        <v>387</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>159</v>
       </c>
       <c r="H40" s="2">
         <v>22</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>8</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>112</v>
+        <v>387</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H41" s="2">
         <v>22</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>164</v>
+        <v>389</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
@@ -3413,375 +3521,391 @@
         <v>9</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>112</v>
+        <v>387</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H42" s="2">
         <v>142</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>9</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>112</v>
+        <v>387</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H43" s="2">
         <v>521</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J43" s="2"/>
       <c r="K43" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>9</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>112</v>
+        <v>387</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H44" s="2">
         <v>146</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>10</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>181</v>
+        <v>390</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H45" s="2">
         <v>170</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J45" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L45" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="K45" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L45" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="M45" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>120</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>10</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>185</v>
-      </c>
       <c r="D46" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H46" s="2">
         <v>162</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>10</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>181</v>
+        <v>390</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H47" s="2">
         <v>531</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J47" s="2"/>
       <c r="K47" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>10</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>181</v>
+        <v>390</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H48" s="2">
         <v>171</v>
       </c>
       <c r="I48" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J48" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="J48" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="K48" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L48" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="L48" s="2" t="s">
+      <c r="M48" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="M48" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="N48" s="2"/>
+      <c r="N48" s="2" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>10</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>181</v>
+        <v>390</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H49" s="2">
         <v>30</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J49" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L49" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="K49" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L49" s="2" t="s">
+      <c r="M49" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="M49" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="N49" s="2"/>
+      <c r="N49" s="2" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>10</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>181</v>
+        <v>390</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H50" s="2">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J50" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L50" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="K50" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L50" s="2" t="s">
+      <c r="M50" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="M50" s="2" t="s">
-        <v>153</v>
-      </c>
       <c r="N50" s="2" t="s">
-        <v>156</v>
+        <v>392</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
@@ -3789,85 +3913,87 @@
         <v>10</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>181</v>
+        <v>390</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H51" s="2">
         <v>32</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="N51" s="2" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>10</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>181</v>
+        <v>390</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H52" s="2">
         <v>32</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>164</v>
+        <v>392</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
@@ -3875,375 +4001,391 @@
         <v>11</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>181</v>
+        <v>390</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="H53" s="2">
         <v>163</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>11</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>181</v>
+        <v>390</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="H54" s="2">
         <v>533</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>11</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>181</v>
+        <v>390</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H55" s="2">
         <v>166</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>13</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>210</v>
+        <v>393</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H56" s="2">
         <v>191</v>
       </c>
       <c r="I56" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J56" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="J56" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="K56" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L56" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="L56" s="2" t="s">
+      <c r="M56" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="M56" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="N56" s="2"/>
+      <c r="N56" s="2" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>13</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>210</v>
+        <v>393</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H57" s="2">
         <v>184</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J57" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L57" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="K57" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L57" s="2" t="s">
+      <c r="M57" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="M57" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="N57" s="2"/>
+      <c r="N57" s="2" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>13</v>
       </c>
       <c r="B58" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>215</v>
-      </c>
       <c r="D58" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H58" s="2">
         <v>544</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J58" s="2"/>
       <c r="K58" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>126</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>13</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>210</v>
+        <v>393</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H59" s="2">
         <v>190</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J59" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L59" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="K59" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L59" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="M59" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>120</v>
+      </c>
+      <c r="N59" s="2" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>13</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>210</v>
+        <v>393</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H60" s="2">
         <v>40</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J60" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L60" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="K60" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L60" s="2" t="s">
+      <c r="M60" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="M60" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="N60" s="2"/>
+      <c r="N60" s="2" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>13</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>210</v>
+        <v>393</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H61" s="2">
         <v>40</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J61" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L61" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="K61" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L61" s="2" t="s">
+      <c r="M61" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="M61" s="2" t="s">
-        <v>153</v>
-      </c>
       <c r="N61" s="2" t="s">
-        <v>156</v>
+        <v>395</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
@@ -4251,85 +4393,87 @@
         <v>13</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>210</v>
+        <v>393</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H62" s="2">
         <v>42</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>13</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>210</v>
+        <v>393</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H63" s="2">
         <v>42</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>164</v>
+        <v>395</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
@@ -4337,375 +4481,391 @@
         <v>14</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>210</v>
+        <v>393</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H64" s="2">
         <v>182</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>14</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>210</v>
+        <v>393</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H65" s="2">
         <v>541</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="N65" s="2" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>14</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>210</v>
+        <v>393</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H66" s="2">
         <v>186</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>15</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>233</v>
+        <v>396</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="G67" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J67" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="H67" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="J67" s="2" t="s">
+      <c r="K67" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L67" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="K67" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L67" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="M67" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>120</v>
+      </c>
+      <c r="N67" s="2" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>15</v>
       </c>
       <c r="B68" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E68" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>239</v>
-      </c>
       <c r="F68" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="G68" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="M68" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="H68" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="I68" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="J68" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="K68" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L68" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="M68" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="N68" s="2"/>
+      <c r="N68" s="2" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>15</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>233</v>
+        <v>396</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H69" s="2">
         <v>551</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="N69" s="2" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>15</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>233</v>
+        <v>396</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="I70" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J70" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="J70" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="K70" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L70" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="L70" s="2" t="s">
+      <c r="M70" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="M70" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="N70" s="2"/>
+      <c r="N70" s="2" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>15</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>233</v>
+        <v>396</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H71" s="2">
         <v>50</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J71" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L71" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="K71" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L71" s="2" t="s">
+      <c r="M71" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="M71" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="N71" s="2"/>
+      <c r="N71" s="2" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>15</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>233</v>
+        <v>396</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H72" s="2">
         <v>50</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J72" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L72" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="K72" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L72" s="2" t="s">
+      <c r="M72" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="M72" s="2" t="s">
-        <v>153</v>
-      </c>
       <c r="N72" s="2" t="s">
-        <v>156</v>
+        <v>398</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
@@ -4713,85 +4873,87 @@
         <v>15</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>233</v>
+        <v>396</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H73" s="2">
         <v>52</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="N73" s="2" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>15</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>233</v>
+        <v>396</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H74" s="2">
         <v>52</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>164</v>
+        <v>398</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
@@ -4799,375 +4961,391 @@
         <v>16</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>233</v>
+        <v>396</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="N75" s="2" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>16</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>233</v>
+        <v>396</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="H76" s="2">
         <v>553</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J76" s="2"/>
       <c r="K76" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="N76" s="2" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>16</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>233</v>
+        <v>396</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="G77" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="M77" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="H77" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="I77" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="J77" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="K77" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L77" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="M77" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="N77" s="2"/>
+      <c r="N77" s="2" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>18</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>262</v>
+        <v>399</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="I78" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J78" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="J78" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="K78" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L78" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="L78" s="2" t="s">
+      <c r="M78" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="M78" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="N78" s="2"/>
+      <c r="N78" s="2" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>18</v>
       </c>
       <c r="B79" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H79" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="C79" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="G79" s="2" t="s">
+      <c r="I79" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J79" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="H79" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="I79" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="J79" s="2" t="s">
+      <c r="K79" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L79" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="K79" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L79" s="2" t="s">
+      <c r="M79" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="M79" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="N79" s="2"/>
+      <c r="N79" s="2" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>18</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>262</v>
+        <v>399</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H80" s="2">
         <v>564</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J80" s="2"/>
       <c r="K80" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>126</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>18</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>262</v>
+        <v>399</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="G81" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J81" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="H81" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="I81" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="J81" s="2" t="s">
+      <c r="K81" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L81" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="K81" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L81" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="M81" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>120</v>
+      </c>
+      <c r="N81" s="2" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>18</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>262</v>
+        <v>399</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H82" s="2">
         <v>60</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J82" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L82" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="K82" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L82" s="2" t="s">
+      <c r="M82" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="M82" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="N82" s="2"/>
+      <c r="N82" s="2" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>18</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>262</v>
+        <v>399</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H83" s="2">
         <v>60</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J83" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L83" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="K83" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L83" s="2" t="s">
+      <c r="M83" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="M83" s="2" t="s">
-        <v>153</v>
-      </c>
       <c r="N83" s="2" t="s">
-        <v>156</v>
+        <v>401</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">
@@ -5175,85 +5353,87 @@
         <v>18</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>262</v>
+        <v>399</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H84" s="2">
         <v>62</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="N84" s="2" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>18</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>262</v>
+        <v>399</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H85" s="2">
         <v>62</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>164</v>
+        <v>401</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.3">
@@ -5261,375 +5441,391 @@
         <v>19</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>262</v>
+        <v>399</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="G86" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="M86" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="H86" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="I86" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="J86" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="K86" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L86" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="M86" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="N86" s="2"/>
+      <c r="N86" s="2" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>19</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>262</v>
+        <v>399</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H87" s="2">
         <v>561</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J87" s="2"/>
       <c r="K87" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="N87" s="2" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>19</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>262</v>
+        <v>399</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="G88" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="M88" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="H88" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="I88" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="J88" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="K88" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L88" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="M88" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="N88" s="2"/>
+      <c r="N88" s="2" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>20</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>291</v>
+        <v>402</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="G89" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J89" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="H89" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="I89" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="J89" s="2" t="s">
+      <c r="K89" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L89" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="K89" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L89" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="M89" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>120</v>
+      </c>
+      <c r="N89" s="2" t="s">
+        <v>403</v>
+      </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>20</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>291</v>
+        <v>402</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H90" s="3">
         <v>100</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N90" s="2" t="s">
+        <v>403</v>
+      </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>20</v>
       </c>
       <c r="B91" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E91" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C91" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>299</v>
-      </c>
       <c r="F91" s="2" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H91" s="2">
         <v>571</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J91" s="2"/>
       <c r="K91" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="N91" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="N91" s="2" t="s">
+        <v>403</v>
+      </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>20</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>291</v>
+        <v>402</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F92" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H92" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="G92" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>302</v>
-      </c>
       <c r="I92" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J92" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="J92" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="K92" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L92" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="L92" s="2" t="s">
+      <c r="M92" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="M92" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="N92" s="2"/>
+      <c r="N92" s="2" t="s">
+        <v>403</v>
+      </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>20</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>291</v>
+        <v>402</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H93" s="2">
         <v>70</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J93" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K93" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L93" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="K93" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L93" s="2" t="s">
+      <c r="M93" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="M93" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="N93" s="2"/>
+      <c r="N93" s="2" t="s">
+        <v>403</v>
+      </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>20</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>291</v>
+        <v>402</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H94" s="2">
         <v>70</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J94" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K94" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L94" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="K94" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L94" s="2" t="s">
+      <c r="M94" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="M94" s="2" t="s">
-        <v>153</v>
-      </c>
       <c r="N94" s="2" t="s">
-        <v>156</v>
+        <v>404</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.3">
@@ -5637,85 +5833,87 @@
         <v>20</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>291</v>
+        <v>402</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H95" s="2">
         <v>72</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="N95" s="2" t="s">
+        <v>403</v>
+      </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>20</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>291</v>
+        <v>402</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H96" s="2">
         <v>72</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>164</v>
+        <v>404</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.3">
@@ -5723,375 +5921,391 @@
         <v>21</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>291</v>
+        <v>402</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="H97" s="3">
         <v>1000</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="N97" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="N97" s="2" t="s">
+        <v>403</v>
+      </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>21</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>291</v>
+        <v>402</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="H98" s="2">
         <v>573</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J98" s="2"/>
       <c r="K98" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="N98" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="N98" s="2" t="s">
+        <v>403</v>
+      </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>21</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>291</v>
+        <v>402</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H99" s="3">
         <v>1000000</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="N99" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="N99" s="2" t="s">
+        <v>403</v>
+      </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>23</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>317</v>
+        <v>405</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H100" s="2">
         <v>211</v>
       </c>
       <c r="I100" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J100" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="J100" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="K100" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L100" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="L100" s="2" t="s">
+      <c r="M100" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="M100" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="N100" s="2"/>
+      <c r="N100" s="2" t="s">
+        <v>406</v>
+      </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>23</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>317</v>
+        <v>405</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H101" s="2">
         <v>204</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J101" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="K101" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L101" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="K101" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L101" s="2" t="s">
+      <c r="M101" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="M101" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="N101" s="2"/>
+      <c r="N101" s="2" t="s">
+        <v>406</v>
+      </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>23</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>317</v>
+        <v>405</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H102" s="2">
         <v>584</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J102" s="2"/>
       <c r="K102" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="N102" s="2"/>
+        <v>126</v>
+      </c>
+      <c r="N102" s="2" t="s">
+        <v>406</v>
+      </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>23</v>
       </c>
       <c r="B103" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E103" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="C103" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>326</v>
-      </c>
       <c r="F103" s="2" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H103" s="2">
         <v>210</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J103" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="K103" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L103" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="K103" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L103" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="M103" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>120</v>
+      </c>
+      <c r="N103" s="2" t="s">
+        <v>406</v>
+      </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>23</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>317</v>
+        <v>405</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H104" s="2">
         <v>80</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J104" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K104" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L104" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="K104" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L104" s="2" t="s">
+      <c r="M104" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="M104" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="N104" s="2"/>
+      <c r="N104" s="2" t="s">
+        <v>406</v>
+      </c>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>23</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>317</v>
+        <v>405</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H105" s="2">
         <v>80</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J105" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K105" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L105" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="K105" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L105" s="2" t="s">
+      <c r="M105" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="M105" s="2" t="s">
-        <v>153</v>
-      </c>
       <c r="N105" s="2" t="s">
-        <v>156</v>
+        <v>407</v>
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.3">
@@ -6099,85 +6313,87 @@
         <v>23</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>317</v>
+        <v>405</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H106" s="2">
         <v>82</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L106" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="N106" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="N106" s="2" t="s">
+        <v>406</v>
+      </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
         <v>23</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>317</v>
+        <v>405</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H107" s="2">
         <v>82</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N107" s="2" t="s">
-        <v>164</v>
+        <v>407</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.3">
@@ -6185,375 +6401,391 @@
         <v>24</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>317</v>
+        <v>405</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H108" s="2">
         <v>202</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="N108" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N108" s="2" t="s">
+        <v>406</v>
+      </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
         <v>24</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>317</v>
+        <v>405</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H109" s="2">
         <v>581</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J109" s="2"/>
       <c r="K109" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L109" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="N109" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="N109" s="2" t="s">
+        <v>406</v>
+      </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
         <v>24</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>317</v>
+        <v>405</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H110" s="2">
         <v>206</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L110" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="N110" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="N110" s="2" t="s">
+        <v>406</v>
+      </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
         <v>25</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>341</v>
+        <v>408</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H111" s="2">
         <v>230</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J111" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="K111" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L111" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="K111" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L111" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="M111" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="N111" s="2"/>
+        <v>120</v>
+      </c>
+      <c r="N111" s="2" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
         <v>25</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>341</v>
+        <v>408</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H112" s="2">
         <v>222</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L112" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="N112" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N112" s="2" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
         <v>25</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>341</v>
+        <v>408</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H113" s="2">
         <v>591</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J113" s="2"/>
       <c r="K113" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L113" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="N113" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="N113" s="2" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
         <v>25</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>341</v>
+        <v>408</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H114" s="2">
         <v>231</v>
       </c>
       <c r="I114" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J114" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="J114" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="K114" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L114" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="L114" s="2" t="s">
+      <c r="M114" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="M114" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="N114" s="2"/>
+      <c r="N114" s="2" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
         <v>25</v>
       </c>
       <c r="B115" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C115" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C115" s="2" t="s">
-        <v>351</v>
-      </c>
       <c r="D115" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H115" s="2">
         <v>90</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J115" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K115" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L115" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="K115" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L115" s="2" t="s">
+      <c r="M115" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="M115" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="N115" s="2"/>
+      <c r="N115" s="2" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
         <v>25</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>341</v>
+        <v>408</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H116" s="2">
         <v>90</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J116" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K116" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L116" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="K116" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L116" s="2" t="s">
+      <c r="M116" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="M116" s="2" t="s">
-        <v>153</v>
-      </c>
       <c r="N116" s="2" t="s">
-        <v>156</v>
+        <v>410</v>
       </c>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.3">
@@ -6561,85 +6793,87 @@
         <v>25</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>341</v>
+        <v>408</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H117" s="2">
         <v>92</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L117" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="N117" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="N117" s="2" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
         <v>25</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>341</v>
+        <v>408</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H118" s="2">
         <v>92</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L118" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N118" s="2" t="s">
-        <v>164</v>
+        <v>410</v>
       </c>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.3">
@@ -6647,124 +6881,130 @@
         <v>26</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>341</v>
+        <v>408</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="H119" s="2">
         <v>223</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="K119" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L119" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="N119" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="N119" s="2" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
         <v>26</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>341</v>
+        <v>408</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="H120" s="2">
         <v>593</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J120" s="2"/>
       <c r="K120" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L120" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="N120" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="N120" s="2" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
         <v>26</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>341</v>
+        <v>408</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H121" s="2">
         <v>226</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="K121" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L121" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="N121" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="N121" s="2" t="s">
+        <v>409</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N1" xr:uid="{3B5293FE-149D-4E2F-A4D6-BCFE466472CA}"/>
@@ -6775,7 +7015,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAA8FA51-8502-4285-A9FD-F9EDA816E8B5}">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.625" customWidth="1"/>
@@ -6784,36 +7024,36 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="B3" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="B4" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="B5" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="B6" s="5">
         <v>46256</v>
@@ -6821,105 +7061,134 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="B9" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="B10" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="B11" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="B12" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="B15" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="B16" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="B17" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="B20" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="B21" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="B22" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B23" t="s">
-        <v>395</v>
+        <v>385</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>412</v>
+      </c>
+      <c r="B26" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>414</v>
+      </c>
+      <c r="B27" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>416</v>
+      </c>
+      <c r="B28" t="s">
+        <v>417</v>
       </c>
     </row>
   </sheetData>

--- a/PLC원본_구ECS_영역매칭표_20260822.xlsx
+++ b/PLC원본_구ECS_영역매칭표_20260822.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\LGLS\Renewal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{557F5659-81DC-41FF-ADD4-C14B12FF5D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C588F8AC-CCB9-4721-B164-766F4225679D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{30F2DBE0-EFF0-40FE-BF74-BD8413AA3908}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{30F2DBE0-EFF0-40FE-BF74-BD8413AA3908}"/>
   </bookViews>
   <sheets>
     <sheet name="영역 매칭표" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'영역 매칭표'!$A$1:$N$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'영역 매칭표'!$A$1:$M$121</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'영역 매칭표'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="423">
   <si>
     <t>슬라이드</t>
   </si>
@@ -1308,6 +1310,26 @@
   </si>
   <si>
     <t>Reset Alarm Code 의 'D0xxx : X' 에서 X 의 의미, 통로 C/V 슬라이드의 Direction Mode Check 취소선 — PLC 확인 필요 (원본 PPT V1.2 에 붉은 질의 표기)</t>
+  </si>
+  <si>
+    <t>ALARM_SET_REPORT</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOAD_COMPLETE_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PALLET_EXIST01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PALLET_EXIST_FLAG_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PALLET_EXIST_FLAG_02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1749,7 +1771,7 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.625" customWidth="1"/>
+    <col min="2" max="2" width="34.625" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="11.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.125" bestFit="1" customWidth="1"/>
@@ -1757,14 +1779,14 @@
     <col min="7" max="7" width="22.75" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="9.625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="42.625" customWidth="1"/>
     <col min="13" max="13" width="20.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="113" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1828,7 +1850,7 @@
         <v>18</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>19</v>
+        <v>418</v>
       </c>
       <c r="H2" s="2">
         <v>312</v>
@@ -3098,7 +3120,7 @@
         <v>114</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>115</v>
+        <v>422</v>
       </c>
       <c r="H32" s="2">
         <v>151</v>
@@ -3316,7 +3338,7 @@
         <v>114</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>143</v>
+        <v>421</v>
       </c>
       <c r="H37" s="2">
         <v>150</v>
@@ -3360,7 +3382,7 @@
         <v>114</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>149</v>
+        <v>420</v>
       </c>
       <c r="H38" s="2">
         <v>20</v>
@@ -3710,7 +3732,7 @@
         <v>180</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>164</v>
+        <v>419</v>
       </c>
       <c r="H46" s="2">
         <v>162</v>
@@ -7009,7 +7031,11 @@
   </sheetData>
   <autoFilter ref="A1:N1" xr:uid="{3B5293FE-149D-4E2F-A4D6-BCFE466472CA}"/>
   <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="70" orientation="landscape" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="13" max="120" man="1"/>
+  </colBreaks>
 </worksheet>
 </file>
 
